--- a/Data/Equip.xlsx
+++ b/Data/Equip.xlsx
@@ -1,34 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF706C1F-A5BA-414F-B289-F13398F2C78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="47520" yWindow="2445" windowWidth="25935" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equip" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Equip" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+  <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>EquipType</t>
+  </si>
+  <si>
+    <t>BaseAtk</t>
+  </si>
+  <si>
+    <t>BaseDef</t>
+  </si>
+  <si>
+    <t>BaseHp</t>
+  </si>
+  <si>
+    <t>Sword</t>
+  </si>
+  <si>
+    <t>Helmet</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>Glove</t>
+  </si>
+  <si>
+    <t>Shoes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cape </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +96,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,131 +398,236 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col min="1" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ItemId</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>EquipType</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Rarity</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>BaseAtk</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>BaseDef</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>BaseHp</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>EnhanceStatRatePerLevel</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>110010001</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Sword</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Training Sword</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3101</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>110020001</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Helmet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Leather Helm</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="E3">
         <v>10</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.05</v>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>3105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>3106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3201</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>3202</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>3203</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>50</v>
+      </c>
+      <c r="E10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>3204</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>3205</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>30</v>
+      </c>
+      <c r="E12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>3206</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>40</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Data/Equip.xlsx
+++ b/Data/Equip.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\Equip_System_Package\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF706C1F-A5BA-414F-B289-F13398F2C78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149332F2-2539-4589-A917-D21A0A933497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47520" yWindow="2445" windowWidth="25935" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39915" yWindow="1515" windowWidth="22515" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equip" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="246">
   <si>
     <t>ItemId</t>
   </si>
@@ -28,13 +28,718 @@
     <t>EquipType</t>
   </si>
   <si>
-    <t>BaseAtk</t>
-  </si>
-  <si>
-    <t>BaseDef</t>
-  </si>
-  <si>
-    <t>BaseHp</t>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>BaseStats</t>
+  </si>
+  <si>
+    <t>Common_Sword_1</t>
+  </si>
+  <si>
+    <t>Attack=6|AttackSpeed=0.018</t>
+  </si>
+  <si>
+    <t>Common_Sword_2</t>
+  </si>
+  <si>
+    <t>Attack=7|AttackSpeed=0.018</t>
+  </si>
+  <si>
+    <t>Common_Sword_3</t>
+  </si>
+  <si>
+    <t>Attack=6|CritChance=1.2</t>
+  </si>
+  <si>
+    <t>Common_Helmet_1</t>
+  </si>
+  <si>
+    <t>Defence=4|HP=26</t>
+  </si>
+  <si>
+    <t>Common_Helmet_2</t>
+  </si>
+  <si>
+    <t>Defence=4|HP=24</t>
+  </si>
+  <si>
+    <t>Common_Helmet_3</t>
+  </si>
+  <si>
+    <t>Common_Armor_1</t>
+  </si>
+  <si>
+    <t>Defence=6|HP=53</t>
+  </si>
+  <si>
+    <t>Common_Armor_2</t>
+  </si>
+  <si>
+    <t>Defence=6|HP=48</t>
+  </si>
+  <si>
+    <t>Common_Armor_3</t>
+  </si>
+  <si>
+    <t>Defence=7|HP=48</t>
+  </si>
+  <si>
+    <t>Common_Glove_1</t>
+  </si>
+  <si>
+    <t>Attack=4|AttackSpeed=0.03</t>
+  </si>
+  <si>
+    <t>Common_Glove_2</t>
+  </si>
+  <si>
+    <t>Attack=4|AttackSpeed=0.033</t>
+  </si>
+  <si>
+    <t>Common_Glove_3</t>
+  </si>
+  <si>
+    <t>Common_Shoes_1</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.03|Evasion=1.8</t>
+  </si>
+  <si>
+    <t>Common_Shoes_2</t>
+  </si>
+  <si>
+    <t>Common_Shoes_3</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.033|Evasion=1.98</t>
+  </si>
+  <si>
+    <t>Common_Cape_1</t>
+  </si>
+  <si>
+    <t>HP=33|CritDmgIncrease=0.06</t>
+  </si>
+  <si>
+    <t>Common_Cape_2</t>
+  </si>
+  <si>
+    <t>HP=30|CritDmgIncrease=0.066</t>
+  </si>
+  <si>
+    <t>Common_Cape_3</t>
+  </si>
+  <si>
+    <t>HP=30|CritDmgIncrease=0.06</t>
+  </si>
+  <si>
+    <t>Uncommon_Sword_1</t>
+  </si>
+  <si>
+    <t>Attack=8|AttackSpeed=0.024</t>
+  </si>
+  <si>
+    <t>Uncommon_Sword_2</t>
+  </si>
+  <si>
+    <t>Attack=9|AttackSpeed=0.024</t>
+  </si>
+  <si>
+    <t>Uncommon_Sword_3</t>
+  </si>
+  <si>
+    <t>Attack=8|CritChance=1.6</t>
+  </si>
+  <si>
+    <t>Uncommon_Helmet_1</t>
+  </si>
+  <si>
+    <t>Defence=5|HP=35</t>
+  </si>
+  <si>
+    <t>Uncommon_Helmet_2</t>
+  </si>
+  <si>
+    <t>Defence=5|HP=32</t>
+  </si>
+  <si>
+    <t>Uncommon_Helmet_3</t>
+  </si>
+  <si>
+    <t>Uncommon_Armor_1</t>
+  </si>
+  <si>
+    <t>Defence=8|HP=70</t>
+  </si>
+  <si>
+    <t>Uncommon_Armor_2</t>
+  </si>
+  <si>
+    <t>Defence=8|HP=64</t>
+  </si>
+  <si>
+    <t>Uncommon_Armor_3</t>
+  </si>
+  <si>
+    <t>Defence=9|HP=64</t>
+  </si>
+  <si>
+    <t>Uncommon_Glove_1</t>
+  </si>
+  <si>
+    <t>Attack=5|AttackSpeed=0.04</t>
+  </si>
+  <si>
+    <t>Uncommon_Glove_2</t>
+  </si>
+  <si>
+    <t>Attack=5|AttackSpeed=0.044</t>
+  </si>
+  <si>
+    <t>Uncommon_Glove_3</t>
+  </si>
+  <si>
+    <t>Uncommon_Shoes_1</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.04|Evasion=2.4</t>
+  </si>
+  <si>
+    <t>Uncommon_Shoes_2</t>
+  </si>
+  <si>
+    <t>Uncommon_Shoes_3</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.044|Evasion=2.64</t>
+  </si>
+  <si>
+    <t>Uncommon_Cape_1</t>
+  </si>
+  <si>
+    <t>HP=44|CritDmgIncrease=0.08</t>
+  </si>
+  <si>
+    <t>Uncommon_Cape_2</t>
+  </si>
+  <si>
+    <t>HP=40|CritDmgIncrease=0.088</t>
+  </si>
+  <si>
+    <t>Uncommon_Cape_3</t>
+  </si>
+  <si>
+    <t>HP=40|CritDmgIncrease=0.08</t>
+  </si>
+  <si>
+    <t>Rare_Sword_1</t>
+  </si>
+  <si>
+    <t>Attack=10|AttackSpeed=0.03</t>
+  </si>
+  <si>
+    <t>Rare_Sword_2</t>
+  </si>
+  <si>
+    <t>Attack=11|AttackSpeed=0.03</t>
+  </si>
+  <si>
+    <t>Rare_Sword_3</t>
+  </si>
+  <si>
+    <t>Attack=10|CritChance=2.0</t>
+  </si>
+  <si>
+    <t>Rare_Helmet_1</t>
+  </si>
+  <si>
+    <t>Defence=6|HP=44</t>
+  </si>
+  <si>
+    <t>Rare_Helmet_2</t>
+  </si>
+  <si>
+    <t>Defence=6|HP=40</t>
+  </si>
+  <si>
+    <t>Rare_Helmet_3</t>
+  </si>
+  <si>
+    <t>Defence=7|HP=40</t>
+  </si>
+  <si>
+    <t>Rare_Armor_1</t>
+  </si>
+  <si>
+    <t>Defence=10|HP=88</t>
+  </si>
+  <si>
+    <t>Rare_Armor_2</t>
+  </si>
+  <si>
+    <t>Defence=10|HP=80</t>
+  </si>
+  <si>
+    <t>Rare_Armor_3</t>
+  </si>
+  <si>
+    <t>Defence=11|HP=80</t>
+  </si>
+  <si>
+    <t>Rare_Glove_1</t>
+  </si>
+  <si>
+    <t>Attack=6|AttackSpeed=0.05</t>
+  </si>
+  <si>
+    <t>Rare_Glove_2</t>
+  </si>
+  <si>
+    <t>Attack=7|AttackSpeed=0.055</t>
+  </si>
+  <si>
+    <t>Rare_Glove_3</t>
+  </si>
+  <si>
+    <t>Rare_Shoes_1</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.05|Evasion=3.0</t>
+  </si>
+  <si>
+    <t>Rare_Shoes_2</t>
+  </si>
+  <si>
+    <t>Rare_Shoes_3</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.055|Evasion=3.3</t>
+  </si>
+  <si>
+    <t>Rare_Cape_1</t>
+  </si>
+  <si>
+    <t>HP=55|CritDmgIncrease=0.1</t>
+  </si>
+  <si>
+    <t>Rare_Cape_2</t>
+  </si>
+  <si>
+    <t>HP=50|CritDmgIncrease=0.11</t>
+  </si>
+  <si>
+    <t>Rare_Cape_3</t>
+  </si>
+  <si>
+    <t>HP=50|CritDmgIncrease=0.1</t>
+  </si>
+  <si>
+    <t>Epic_Sword_1</t>
+  </si>
+  <si>
+    <t>Attack=15|AttackSpeed=0.045</t>
+  </si>
+  <si>
+    <t>Epic_Sword_2</t>
+  </si>
+  <si>
+    <t>Attack=16|AttackSpeed=0.045</t>
+  </si>
+  <si>
+    <t>Epic_Sword_3</t>
+  </si>
+  <si>
+    <t>Attack=15|CritChance=3.0</t>
+  </si>
+  <si>
+    <t>Epic_Helmet_1</t>
+  </si>
+  <si>
+    <t>Defence=9|HP=66</t>
+  </si>
+  <si>
+    <t>Epic_Helmet_2</t>
+  </si>
+  <si>
+    <t>Defence=9|HP=60</t>
+  </si>
+  <si>
+    <t>Epic_Helmet_3</t>
+  </si>
+  <si>
+    <t>Defence=10|HP=60</t>
+  </si>
+  <si>
+    <t>Epic_Armor_1</t>
+  </si>
+  <si>
+    <t>Defence=15|HP=132</t>
+  </si>
+  <si>
+    <t>Epic_Armor_2</t>
+  </si>
+  <si>
+    <t>Defence=15|HP=120</t>
+  </si>
+  <si>
+    <t>Epic_Armor_3</t>
+  </si>
+  <si>
+    <t>Defence=16|HP=120</t>
+  </si>
+  <si>
+    <t>Epic_Glove_1</t>
+  </si>
+  <si>
+    <t>Attack=9|AttackSpeed=0.075</t>
+  </si>
+  <si>
+    <t>Epic_Glove_2</t>
+  </si>
+  <si>
+    <t>Attack=10|AttackSpeed=0.083</t>
+  </si>
+  <si>
+    <t>Epic_Glove_3</t>
+  </si>
+  <si>
+    <t>Epic_Shoes_1</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.075|Evasion=4.5</t>
+  </si>
+  <si>
+    <t>Epic_Shoes_2</t>
+  </si>
+  <si>
+    <t>Epic_Shoes_3</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.083|Evasion=4.95</t>
+  </si>
+  <si>
+    <t>Epic_Cape_1</t>
+  </si>
+  <si>
+    <t>HP=82|CritDmgIncrease=0.15</t>
+  </si>
+  <si>
+    <t>Epic_Cape_2</t>
+  </si>
+  <si>
+    <t>HP=75|CritDmgIncrease=0.165</t>
+  </si>
+  <si>
+    <t>Epic_Cape_3</t>
+  </si>
+  <si>
+    <t>HP=75|CritDmgIncrease=0.15</t>
+  </si>
+  <si>
+    <t>Legendary_Sword_1</t>
+  </si>
+  <si>
+    <t>Attack=22|AttackSpeed=0.066</t>
+  </si>
+  <si>
+    <t>Legendary_Sword_2</t>
+  </si>
+  <si>
+    <t>Attack=24|AttackSpeed=0.066</t>
+  </si>
+  <si>
+    <t>Legendary_Sword_3</t>
+  </si>
+  <si>
+    <t>Attack=22|CritChance=4.4</t>
+  </si>
+  <si>
+    <t>Legendary_Helmet_1</t>
+  </si>
+  <si>
+    <t>Defence=13|HP=97</t>
+  </si>
+  <si>
+    <t>Legendary_Helmet_2</t>
+  </si>
+  <si>
+    <t>Defence=13|HP=88</t>
+  </si>
+  <si>
+    <t>Legendary_Helmet_3</t>
+  </si>
+  <si>
+    <t>Defence=15|HP=88</t>
+  </si>
+  <si>
+    <t>Legendary_Armor_1</t>
+  </si>
+  <si>
+    <t>Defence=22|HP=194</t>
+  </si>
+  <si>
+    <t>Legendary_Armor_2</t>
+  </si>
+  <si>
+    <t>Defence=22|HP=176</t>
+  </si>
+  <si>
+    <t>Legendary_Armor_3</t>
+  </si>
+  <si>
+    <t>Defence=24|HP=176</t>
+  </si>
+  <si>
+    <t>Legendary_Glove_1</t>
+  </si>
+  <si>
+    <t>Attack=13|AttackSpeed=0.11</t>
+  </si>
+  <si>
+    <t>Legendary_Glove_2</t>
+  </si>
+  <si>
+    <t>Attack=15|AttackSpeed=0.121</t>
+  </si>
+  <si>
+    <t>Legendary_Glove_3</t>
+  </si>
+  <si>
+    <t>Legendary_Shoes_1</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.11|Evasion=6.6</t>
+  </si>
+  <si>
+    <t>Legendary_Shoes_2</t>
+  </si>
+  <si>
+    <t>Legendary_Shoes_3</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.121|Evasion=7.26</t>
+  </si>
+  <si>
+    <t>Legendary_Cape_1</t>
+  </si>
+  <si>
+    <t>HP=121|CritDmgIncrease=0.22</t>
+  </si>
+  <si>
+    <t>Legendary_Cape_2</t>
+  </si>
+  <si>
+    <t>HP=110|CritDmgIncrease=0.242</t>
+  </si>
+  <si>
+    <t>Legendary_Cape_3</t>
+  </si>
+  <si>
+    <t>HP=110|CritDmgIncrease=0.22</t>
+  </si>
+  <si>
+    <t>Mythic_Sword_1</t>
+  </si>
+  <si>
+    <t>Attack=32|AttackSpeed=0.096</t>
+  </si>
+  <si>
+    <t>Mythic_Sword_2</t>
+  </si>
+  <si>
+    <t>Attack=35|AttackSpeed=0.096</t>
+  </si>
+  <si>
+    <t>Mythic_Sword_3</t>
+  </si>
+  <si>
+    <t>Attack=32|CritChance=6.4</t>
+  </si>
+  <si>
+    <t>Mythic_Helmet_1</t>
+  </si>
+  <si>
+    <t>Defence=19|HP=141</t>
+  </si>
+  <si>
+    <t>Mythic_Helmet_2</t>
+  </si>
+  <si>
+    <t>Defence=19|HP=128</t>
+  </si>
+  <si>
+    <t>Mythic_Helmet_3</t>
+  </si>
+  <si>
+    <t>Defence=21|HP=128</t>
+  </si>
+  <si>
+    <t>Mythic_Armor_1</t>
+  </si>
+  <si>
+    <t>Defence=32|HP=282</t>
+  </si>
+  <si>
+    <t>Mythic_Armor_2</t>
+  </si>
+  <si>
+    <t>Defence=32|HP=256</t>
+  </si>
+  <si>
+    <t>Mythic_Armor_3</t>
+  </si>
+  <si>
+    <t>Defence=35|HP=256</t>
+  </si>
+  <si>
+    <t>Mythic_Glove_1</t>
+  </si>
+  <si>
+    <t>Attack=19|AttackSpeed=0.16</t>
+  </si>
+  <si>
+    <t>Mythic_Glove_2</t>
+  </si>
+  <si>
+    <t>Attack=21|AttackSpeed=0.176</t>
+  </si>
+  <si>
+    <t>Mythic_Glove_3</t>
+  </si>
+  <si>
+    <t>Mythic_Shoes_1</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.16|Evasion=9.6</t>
+  </si>
+  <si>
+    <t>Mythic_Shoes_2</t>
+  </si>
+  <si>
+    <t>Mythic_Shoes_3</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.176|Evasion=10.56</t>
+  </si>
+  <si>
+    <t>Mythic_Cape_1</t>
+  </si>
+  <si>
+    <t>HP=176|CritDmgIncrease=0.32</t>
+  </si>
+  <si>
+    <t>Mythic_Cape_2</t>
+  </si>
+  <si>
+    <t>HP=160|CritDmgIncrease=0.352</t>
+  </si>
+  <si>
+    <t>Mythic_Cape_3</t>
+  </si>
+  <si>
+    <t>HP=160|CritDmgIncrease=0.32</t>
+  </si>
+  <si>
+    <t>Special_Sword_1</t>
+  </si>
+  <si>
+    <t>Attack=45|AttackSpeed=0.135</t>
+  </si>
+  <si>
+    <t>Special_Sword_2</t>
+  </si>
+  <si>
+    <t>Attack=50|AttackSpeed=0.135</t>
+  </si>
+  <si>
+    <t>Special_Sword_3</t>
+  </si>
+  <si>
+    <t>Attack=45|CritChance=9.0</t>
+  </si>
+  <si>
+    <t>Special_Helmet_1</t>
+  </si>
+  <si>
+    <t>Defence=27|HP=198</t>
+  </si>
+  <si>
+    <t>Special_Helmet_2</t>
+  </si>
+  <si>
+    <t>Defence=27|HP=180</t>
+  </si>
+  <si>
+    <t>Special_Helmet_3</t>
+  </si>
+  <si>
+    <t>Defence=30|HP=180</t>
+  </si>
+  <si>
+    <t>Special_Armor_1</t>
+  </si>
+  <si>
+    <t>Defence=45|HP=396</t>
+  </si>
+  <si>
+    <t>Special_Armor_2</t>
+  </si>
+  <si>
+    <t>Defence=45|HP=360</t>
+  </si>
+  <si>
+    <t>Special_Armor_3</t>
+  </si>
+  <si>
+    <t>Defence=50|HP=360</t>
+  </si>
+  <si>
+    <t>Special_Glove_1</t>
+  </si>
+  <si>
+    <t>Attack=27|AttackSpeed=0.225</t>
+  </si>
+  <si>
+    <t>Special_Glove_2</t>
+  </si>
+  <si>
+    <t>Attack=30|AttackSpeed=0.248</t>
+  </si>
+  <si>
+    <t>Special_Glove_3</t>
+  </si>
+  <si>
+    <t>Special_Shoes_1</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.225|Evasion=13.5</t>
+  </si>
+  <si>
+    <t>Special_Shoes_2</t>
+  </si>
+  <si>
+    <t>Special_Shoes_3</t>
+  </si>
+  <si>
+    <t>MoveSpeed=0.248|Evasion=14.85</t>
+  </si>
+  <si>
+    <t>Special_Cape_1</t>
+  </si>
+  <si>
+    <t>HP=248|CritDmgIncrease=0.45</t>
+  </si>
+  <si>
+    <t>Special_Cape_2</t>
+  </si>
+  <si>
+    <t>HP=225|CritDmgIncrease=0.495</t>
+  </si>
+  <si>
+    <t>Special_Cape_3</t>
+  </si>
+  <si>
+    <t>HP=225|CritDmgIncrease=0.45</t>
   </si>
   <si>
     <t>Sword</t>
@@ -52,20 +757,27 @@
     <t>Shoes</t>
   </si>
   <si>
-    <t xml:space="preserve">Cape </t>
+    <t>Cape</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="8"/>
@@ -83,7 +795,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -91,12 +803,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -399,235 +1129,1790 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="5" width="16" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3111</v>
+      </c>
+      <c r="B2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>3101</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>3102</v>
+        <v>3112</v>
       </c>
       <c r="B3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3113</v>
+      </c>
+      <c r="B4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3121</v>
+      </c>
+      <c r="B5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3103</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>3105</v>
+        <v>3122</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>241</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>3106</v>
+        <v>3123</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>241</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>3201</v>
+        <v>3131</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8">
+        <v>242</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>3132</v>
+      </c>
+      <c r="B9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>3133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>3141</v>
+      </c>
+      <c r="B11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>3142</v>
+      </c>
+      <c r="B12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>3143</v>
+      </c>
+      <c r="B13" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>3151</v>
+      </c>
+      <c r="B14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>3152</v>
+      </c>
+      <c r="B15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>3153</v>
+      </c>
+      <c r="B16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>3161</v>
+      </c>
+      <c r="B17" t="s">
+        <v>245</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>3162</v>
+      </c>
+      <c r="B18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>3163</v>
+      </c>
+      <c r="B19" t="s">
+        <v>245</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>3211</v>
+      </c>
+      <c r="B20" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>3212</v>
+      </c>
+      <c r="B21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>3213</v>
+      </c>
+      <c r="B22" t="s">
+        <v>240</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>3221</v>
+      </c>
+      <c r="B23" t="s">
+        <v>241</v>
+      </c>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>3222</v>
+      </c>
+      <c r="B24" t="s">
+        <v>241</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>3223</v>
+      </c>
+      <c r="B25" t="s">
+        <v>241</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>3231</v>
+      </c>
+      <c r="B26" t="s">
+        <v>242</v>
+      </c>
+      <c r="C26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>3232</v>
+      </c>
+      <c r="B27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C27" t="s">
         <v>50</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>3202</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>20</v>
-      </c>
-      <c r="E9">
+      <c r="D27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>3233</v>
+      </c>
+      <c r="B28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>3241</v>
+      </c>
+      <c r="B29" t="s">
+        <v>243</v>
+      </c>
+      <c r="C29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>3242</v>
+      </c>
+      <c r="B30" t="s">
+        <v>243</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>3243</v>
+      </c>
+      <c r="B31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C31" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>3251</v>
+      </c>
+      <c r="B32" t="s">
+        <v>244</v>
+      </c>
+      <c r="C32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>3252</v>
+      </c>
+      <c r="B33" t="s">
+        <v>244</v>
+      </c>
+      <c r="C33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>3253</v>
+      </c>
+      <c r="B34" t="s">
+        <v>244</v>
+      </c>
+      <c r="C34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>3261</v>
+      </c>
+      <c r="B35" t="s">
+        <v>245</v>
+      </c>
+      <c r="C35" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>3262</v>
+      </c>
+      <c r="B36" t="s">
+        <v>245</v>
+      </c>
+      <c r="C36" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>3263</v>
+      </c>
+      <c r="B37" t="s">
+        <v>245</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>3311</v>
+      </c>
+      <c r="B38" t="s">
+        <v>240</v>
+      </c>
+      <c r="C38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>3312</v>
+      </c>
+      <c r="B39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>3313</v>
+      </c>
+      <c r="B40" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>3321</v>
+      </c>
+      <c r="B41" t="s">
+        <v>241</v>
+      </c>
+      <c r="C41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>3322</v>
+      </c>
+      <c r="B42" t="s">
+        <v>241</v>
+      </c>
+      <c r="C42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>3323</v>
+      </c>
+      <c r="B43" t="s">
+        <v>241</v>
+      </c>
+      <c r="C43" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>3331</v>
+      </c>
+      <c r="B44" t="s">
+        <v>242</v>
+      </c>
+      <c r="C44" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>3332</v>
+      </c>
+      <c r="B45" t="s">
+        <v>242</v>
+      </c>
+      <c r="C45" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>3333</v>
+      </c>
+      <c r="B46" t="s">
+        <v>242</v>
+      </c>
+      <c r="C46" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>3341</v>
+      </c>
+      <c r="B47" t="s">
+        <v>243</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>3342</v>
+      </c>
+      <c r="B48" t="s">
+        <v>243</v>
+      </c>
+      <c r="C48" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>3343</v>
+      </c>
+      <c r="B49" t="s">
+        <v>243</v>
+      </c>
+      <c r="C49" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>3351</v>
+      </c>
+      <c r="B50" t="s">
+        <v>244</v>
+      </c>
+      <c r="C50" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>3352</v>
+      </c>
+      <c r="B51" t="s">
+        <v>244</v>
+      </c>
+      <c r="C51" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>3353</v>
+      </c>
+      <c r="B52" t="s">
+        <v>244</v>
+      </c>
+      <c r="C52" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>3361</v>
+      </c>
+      <c r="B53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C53" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>3362</v>
+      </c>
+      <c r="B54" t="s">
+        <v>245</v>
+      </c>
+      <c r="C54" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>3203</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>50</v>
-      </c>
-      <c r="E10">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>3204</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11">
-        <v>20</v>
-      </c>
-      <c r="D11">
-        <v>20</v>
-      </c>
-      <c r="E11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>3205</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12">
-        <v>10</v>
-      </c>
-      <c r="D12">
-        <v>30</v>
-      </c>
-      <c r="E12">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>3206</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>40</v>
-      </c>
-      <c r="E13">
-        <v>30</v>
+      <c r="D54" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>3363</v>
+      </c>
+      <c r="B55" t="s">
+        <v>245</v>
+      </c>
+      <c r="C55" t="s">
+        <v>102</v>
+      </c>
+      <c r="D55" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>3411</v>
+      </c>
+      <c r="B56" t="s">
+        <v>240</v>
+      </c>
+      <c r="C56" t="s">
+        <v>104</v>
+      </c>
+      <c r="D56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>3412</v>
+      </c>
+      <c r="B57" t="s">
+        <v>240</v>
+      </c>
+      <c r="C57" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>3413</v>
+      </c>
+      <c r="B58" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>3421</v>
+      </c>
+      <c r="B59" t="s">
+        <v>241</v>
+      </c>
+      <c r="C59" t="s">
+        <v>110</v>
+      </c>
+      <c r="D59" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>3422</v>
+      </c>
+      <c r="B60" t="s">
+        <v>241</v>
+      </c>
+      <c r="C60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>3423</v>
+      </c>
+      <c r="B61" t="s">
+        <v>241</v>
+      </c>
+      <c r="C61" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>3431</v>
+      </c>
+      <c r="B62" t="s">
+        <v>242</v>
+      </c>
+      <c r="C62" t="s">
+        <v>116</v>
+      </c>
+      <c r="D62" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>3432</v>
+      </c>
+      <c r="B63" t="s">
+        <v>242</v>
+      </c>
+      <c r="C63" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>3433</v>
+      </c>
+      <c r="B64" t="s">
+        <v>242</v>
+      </c>
+      <c r="C64" t="s">
+        <v>120</v>
+      </c>
+      <c r="D64" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>3441</v>
+      </c>
+      <c r="B65" t="s">
+        <v>243</v>
+      </c>
+      <c r="C65" t="s">
+        <v>122</v>
+      </c>
+      <c r="D65" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>3442</v>
+      </c>
+      <c r="B66" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" t="s">
+        <v>124</v>
+      </c>
+      <c r="D66" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>3443</v>
+      </c>
+      <c r="B67" t="s">
+        <v>243</v>
+      </c>
+      <c r="C67" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>3451</v>
+      </c>
+      <c r="B68" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" t="s">
+        <v>127</v>
+      </c>
+      <c r="D68" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>3452</v>
+      </c>
+      <c r="B69" t="s">
+        <v>244</v>
+      </c>
+      <c r="C69" t="s">
+        <v>129</v>
+      </c>
+      <c r="D69" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>3453</v>
+      </c>
+      <c r="B70" t="s">
+        <v>244</v>
+      </c>
+      <c r="C70" t="s">
+        <v>130</v>
+      </c>
+      <c r="D70" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>3461</v>
+      </c>
+      <c r="B71" t="s">
+        <v>245</v>
+      </c>
+      <c r="C71" t="s">
+        <v>132</v>
+      </c>
+      <c r="D71" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>3462</v>
+      </c>
+      <c r="B72" t="s">
+        <v>245</v>
+      </c>
+      <c r="C72" t="s">
+        <v>134</v>
+      </c>
+      <c r="D72" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>3463</v>
+      </c>
+      <c r="B73" t="s">
+        <v>245</v>
+      </c>
+      <c r="C73" t="s">
+        <v>136</v>
+      </c>
+      <c r="D73" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>3511</v>
+      </c>
+      <c r="B74" t="s">
+        <v>240</v>
+      </c>
+      <c r="C74" t="s">
+        <v>138</v>
+      </c>
+      <c r="D74" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>3512</v>
+      </c>
+      <c r="B75" t="s">
+        <v>240</v>
+      </c>
+      <c r="C75" t="s">
+        <v>140</v>
+      </c>
+      <c r="D75" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>3513</v>
+      </c>
+      <c r="B76" t="s">
+        <v>240</v>
+      </c>
+      <c r="C76" t="s">
+        <v>142</v>
+      </c>
+      <c r="D76" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>3521</v>
+      </c>
+      <c r="B77" t="s">
+        <v>241</v>
+      </c>
+      <c r="C77" t="s">
+        <v>144</v>
+      </c>
+      <c r="D77" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>3522</v>
+      </c>
+      <c r="B78" t="s">
+        <v>241</v>
+      </c>
+      <c r="C78" t="s">
+        <v>146</v>
+      </c>
+      <c r="D78" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>3523</v>
+      </c>
+      <c r="B79" t="s">
+        <v>241</v>
+      </c>
+      <c r="C79" t="s">
+        <v>148</v>
+      </c>
+      <c r="D79" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>3531</v>
+      </c>
+      <c r="B80" t="s">
+        <v>242</v>
+      </c>
+      <c r="C80" t="s">
+        <v>150</v>
+      </c>
+      <c r="D80" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>3532</v>
+      </c>
+      <c r="B81" t="s">
+        <v>242</v>
+      </c>
+      <c r="C81" t="s">
+        <v>152</v>
+      </c>
+      <c r="D81" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>3533</v>
+      </c>
+      <c r="B82" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" t="s">
+        <v>154</v>
+      </c>
+      <c r="D82" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>3541</v>
+      </c>
+      <c r="B83" t="s">
+        <v>243</v>
+      </c>
+      <c r="C83" t="s">
+        <v>156</v>
+      </c>
+      <c r="D83" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>3542</v>
+      </c>
+      <c r="B84" t="s">
+        <v>243</v>
+      </c>
+      <c r="C84" t="s">
+        <v>158</v>
+      </c>
+      <c r="D84" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>3543</v>
+      </c>
+      <c r="B85" t="s">
+        <v>243</v>
+      </c>
+      <c r="C85" t="s">
+        <v>160</v>
+      </c>
+      <c r="D85" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>3551</v>
+      </c>
+      <c r="B86" t="s">
+        <v>244</v>
+      </c>
+      <c r="C86" t="s">
+        <v>161</v>
+      </c>
+      <c r="D86" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>3552</v>
+      </c>
+      <c r="B87" t="s">
+        <v>244</v>
+      </c>
+      <c r="C87" t="s">
+        <v>163</v>
+      </c>
+      <c r="D87" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>3553</v>
+      </c>
+      <c r="B88" t="s">
+        <v>244</v>
+      </c>
+      <c r="C88" t="s">
+        <v>164</v>
+      </c>
+      <c r="D88" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>3561</v>
+      </c>
+      <c r="B89" t="s">
+        <v>245</v>
+      </c>
+      <c r="C89" t="s">
+        <v>166</v>
+      </c>
+      <c r="D89" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>3562</v>
+      </c>
+      <c r="B90" t="s">
+        <v>245</v>
+      </c>
+      <c r="C90" t="s">
+        <v>168</v>
+      </c>
+      <c r="D90" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>3563</v>
+      </c>
+      <c r="B91" t="s">
+        <v>245</v>
+      </c>
+      <c r="C91" t="s">
+        <v>170</v>
+      </c>
+      <c r="D91" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>3611</v>
+      </c>
+      <c r="B92" t="s">
+        <v>240</v>
+      </c>
+      <c r="C92" t="s">
+        <v>172</v>
+      </c>
+      <c r="D92" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>3612</v>
+      </c>
+      <c r="B93" t="s">
+        <v>240</v>
+      </c>
+      <c r="C93" t="s">
+        <v>174</v>
+      </c>
+      <c r="D93" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>3613</v>
+      </c>
+      <c r="B94" t="s">
+        <v>240</v>
+      </c>
+      <c r="C94" t="s">
+        <v>176</v>
+      </c>
+      <c r="D94" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>3621</v>
+      </c>
+      <c r="B95" t="s">
+        <v>241</v>
+      </c>
+      <c r="C95" t="s">
+        <v>178</v>
+      </c>
+      <c r="D95" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>3622</v>
+      </c>
+      <c r="B96" t="s">
+        <v>241</v>
+      </c>
+      <c r="C96" t="s">
+        <v>180</v>
+      </c>
+      <c r="D96" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>3623</v>
+      </c>
+      <c r="B97" t="s">
+        <v>241</v>
+      </c>
+      <c r="C97" t="s">
+        <v>182</v>
+      </c>
+      <c r="D97" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>3631</v>
+      </c>
+      <c r="B98" t="s">
+        <v>242</v>
+      </c>
+      <c r="C98" t="s">
+        <v>184</v>
+      </c>
+      <c r="D98" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>3632</v>
+      </c>
+      <c r="B99" t="s">
+        <v>242</v>
+      </c>
+      <c r="C99" t="s">
+        <v>186</v>
+      </c>
+      <c r="D99" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>3633</v>
+      </c>
+      <c r="B100" t="s">
+        <v>242</v>
+      </c>
+      <c r="C100" t="s">
+        <v>188</v>
+      </c>
+      <c r="D100" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>3641</v>
+      </c>
+      <c r="B101" t="s">
+        <v>243</v>
+      </c>
+      <c r="C101" t="s">
+        <v>190</v>
+      </c>
+      <c r="D101" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>3642</v>
+      </c>
+      <c r="B102" t="s">
+        <v>243</v>
+      </c>
+      <c r="C102" t="s">
+        <v>192</v>
+      </c>
+      <c r="D102" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>3643</v>
+      </c>
+      <c r="B103" t="s">
+        <v>243</v>
+      </c>
+      <c r="C103" t="s">
+        <v>194</v>
+      </c>
+      <c r="D103" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>3651</v>
+      </c>
+      <c r="B104" t="s">
+        <v>244</v>
+      </c>
+      <c r="C104" t="s">
+        <v>195</v>
+      </c>
+      <c r="D104" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>3652</v>
+      </c>
+      <c r="B105" t="s">
+        <v>244</v>
+      </c>
+      <c r="C105" t="s">
+        <v>197</v>
+      </c>
+      <c r="D105" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>3653</v>
+      </c>
+      <c r="B106" t="s">
+        <v>244</v>
+      </c>
+      <c r="C106" t="s">
+        <v>198</v>
+      </c>
+      <c r="D106" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>3661</v>
+      </c>
+      <c r="B107" t="s">
+        <v>245</v>
+      </c>
+      <c r="C107" t="s">
+        <v>200</v>
+      </c>
+      <c r="D107" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>3662</v>
+      </c>
+      <c r="B108" t="s">
+        <v>245</v>
+      </c>
+      <c r="C108" t="s">
+        <v>202</v>
+      </c>
+      <c r="D108" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>3663</v>
+      </c>
+      <c r="B109" t="s">
+        <v>245</v>
+      </c>
+      <c r="C109" t="s">
+        <v>204</v>
+      </c>
+      <c r="D109" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>3711</v>
+      </c>
+      <c r="B110" t="s">
+        <v>240</v>
+      </c>
+      <c r="C110" t="s">
+        <v>206</v>
+      </c>
+      <c r="D110" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>3712</v>
+      </c>
+      <c r="B111" t="s">
+        <v>240</v>
+      </c>
+      <c r="C111" t="s">
+        <v>208</v>
+      </c>
+      <c r="D111" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>3713</v>
+      </c>
+      <c r="B112" t="s">
+        <v>240</v>
+      </c>
+      <c r="C112" t="s">
+        <v>210</v>
+      </c>
+      <c r="D112" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>3721</v>
+      </c>
+      <c r="B113" t="s">
+        <v>241</v>
+      </c>
+      <c r="C113" t="s">
+        <v>212</v>
+      </c>
+      <c r="D113" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>3722</v>
+      </c>
+      <c r="B114" t="s">
+        <v>241</v>
+      </c>
+      <c r="C114" t="s">
+        <v>214</v>
+      </c>
+      <c r="D114" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>3723</v>
+      </c>
+      <c r="B115" t="s">
+        <v>241</v>
+      </c>
+      <c r="C115" t="s">
+        <v>216</v>
+      </c>
+      <c r="D115" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>3731</v>
+      </c>
+      <c r="B116" t="s">
+        <v>242</v>
+      </c>
+      <c r="C116" t="s">
+        <v>218</v>
+      </c>
+      <c r="D116" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>3732</v>
+      </c>
+      <c r="B117" t="s">
+        <v>242</v>
+      </c>
+      <c r="C117" t="s">
+        <v>220</v>
+      </c>
+      <c r="D117" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>3733</v>
+      </c>
+      <c r="B118" t="s">
+        <v>242</v>
+      </c>
+      <c r="C118" t="s">
+        <v>222</v>
+      </c>
+      <c r="D118" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>3741</v>
+      </c>
+      <c r="B119" t="s">
+        <v>243</v>
+      </c>
+      <c r="C119" t="s">
+        <v>224</v>
+      </c>
+      <c r="D119" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>3742</v>
+      </c>
+      <c r="B120" t="s">
+        <v>243</v>
+      </c>
+      <c r="C120" t="s">
+        <v>226</v>
+      </c>
+      <c r="D120" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>3743</v>
+      </c>
+      <c r="B121" t="s">
+        <v>243</v>
+      </c>
+      <c r="C121" t="s">
+        <v>228</v>
+      </c>
+      <c r="D121" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>3751</v>
+      </c>
+      <c r="B122" t="s">
+        <v>244</v>
+      </c>
+      <c r="C122" t="s">
+        <v>229</v>
+      </c>
+      <c r="D122" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>3752</v>
+      </c>
+      <c r="B123" t="s">
+        <v>244</v>
+      </c>
+      <c r="C123" t="s">
+        <v>231</v>
+      </c>
+      <c r="D123" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>3753</v>
+      </c>
+      <c r="B124" t="s">
+        <v>244</v>
+      </c>
+      <c r="C124" t="s">
+        <v>232</v>
+      </c>
+      <c r="D124" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>3761</v>
+      </c>
+      <c r="B125" t="s">
+        <v>245</v>
+      </c>
+      <c r="C125" t="s">
+        <v>234</v>
+      </c>
+      <c r="D125" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>3762</v>
+      </c>
+      <c r="B126" t="s">
+        <v>245</v>
+      </c>
+      <c r="C126" t="s">
+        <v>236</v>
+      </c>
+      <c r="D126" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>3763</v>
+      </c>
+      <c r="B127" t="s">
+        <v>245</v>
+      </c>
+      <c r="C127" t="s">
+        <v>238</v>
+      </c>
+      <c r="D127" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data/Equip.xlsx
+++ b/Data/Equip.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\Equip_System_Package\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149332F2-2539-4589-A917-D21A0A933497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7190AF-29F0-41C4-8BF3-942956568415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39915" yWindow="1515" windowWidth="22515" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equip" sheetId="1" r:id="rId1"/>
@@ -37,21 +37,12 @@
     <t>Common_Sword_1</t>
   </si>
   <si>
-    <t>Attack=6|AttackSpeed=0.018</t>
-  </si>
-  <si>
     <t>Common_Sword_2</t>
   </si>
   <si>
-    <t>Attack=7|AttackSpeed=0.018</t>
-  </si>
-  <si>
     <t>Common_Sword_3</t>
   </si>
   <si>
-    <t>Attack=6|CritChance=1.2</t>
-  </si>
-  <si>
     <t>Common_Helmet_1</t>
   </si>
   <si>
@@ -88,69 +79,39 @@
     <t>Common_Glove_1</t>
   </si>
   <si>
-    <t>Attack=4|AttackSpeed=0.03</t>
-  </si>
-  <si>
     <t>Common_Glove_2</t>
   </si>
   <si>
-    <t>Attack=4|AttackSpeed=0.033</t>
-  </si>
-  <si>
     <t>Common_Glove_3</t>
   </si>
   <si>
     <t>Common_Shoes_1</t>
   </si>
   <si>
-    <t>MoveSpeed=0.03|Evasion=1.8</t>
-  </si>
-  <si>
     <t>Common_Shoes_2</t>
   </si>
   <si>
     <t>Common_Shoes_3</t>
   </si>
   <si>
-    <t>MoveSpeed=0.033|Evasion=1.98</t>
-  </si>
-  <si>
     <t>Common_Cape_1</t>
   </si>
   <si>
-    <t>HP=33|CritDmgIncrease=0.06</t>
-  </si>
-  <si>
     <t>Common_Cape_2</t>
   </si>
   <si>
-    <t>HP=30|CritDmgIncrease=0.066</t>
-  </si>
-  <si>
     <t>Common_Cape_3</t>
   </si>
   <si>
-    <t>HP=30|CritDmgIncrease=0.06</t>
-  </si>
-  <si>
     <t>Uncommon_Sword_1</t>
   </si>
   <si>
-    <t>Attack=8|AttackSpeed=0.024</t>
-  </si>
-  <si>
     <t>Uncommon_Sword_2</t>
   </si>
   <si>
-    <t>Attack=9|AttackSpeed=0.024</t>
-  </si>
-  <si>
     <t>Uncommon_Sword_3</t>
   </si>
   <si>
-    <t>Attack=8|CritChance=1.6</t>
-  </si>
-  <si>
     <t>Uncommon_Helmet_1</t>
   </si>
   <si>
@@ -187,69 +148,39 @@
     <t>Uncommon_Glove_1</t>
   </si>
   <si>
-    <t>Attack=5|AttackSpeed=0.04</t>
-  </si>
-  <si>
     <t>Uncommon_Glove_2</t>
   </si>
   <si>
-    <t>Attack=5|AttackSpeed=0.044</t>
-  </si>
-  <si>
     <t>Uncommon_Glove_3</t>
   </si>
   <si>
     <t>Uncommon_Shoes_1</t>
   </si>
   <si>
-    <t>MoveSpeed=0.04|Evasion=2.4</t>
-  </si>
-  <si>
     <t>Uncommon_Shoes_2</t>
   </si>
   <si>
     <t>Uncommon_Shoes_3</t>
   </si>
   <si>
-    <t>MoveSpeed=0.044|Evasion=2.64</t>
-  </si>
-  <si>
     <t>Uncommon_Cape_1</t>
   </si>
   <si>
-    <t>HP=44|CritDmgIncrease=0.08</t>
-  </si>
-  <si>
     <t>Uncommon_Cape_2</t>
   </si>
   <si>
-    <t>HP=40|CritDmgIncrease=0.088</t>
-  </si>
-  <si>
     <t>Uncommon_Cape_3</t>
   </si>
   <si>
-    <t>HP=40|CritDmgIncrease=0.08</t>
-  </si>
-  <si>
     <t>Rare_Sword_1</t>
   </si>
   <si>
-    <t>Attack=10|AttackSpeed=0.03</t>
-  </si>
-  <si>
     <t>Rare_Sword_2</t>
   </si>
   <si>
-    <t>Attack=11|AttackSpeed=0.03</t>
-  </si>
-  <si>
     <t>Rare_Sword_3</t>
   </si>
   <si>
-    <t>Attack=10|CritChance=2.0</t>
-  </si>
-  <si>
     <t>Rare_Helmet_1</t>
   </si>
   <si>
@@ -289,69 +220,39 @@
     <t>Rare_Glove_1</t>
   </si>
   <si>
-    <t>Attack=6|AttackSpeed=0.05</t>
-  </si>
-  <si>
     <t>Rare_Glove_2</t>
   </si>
   <si>
-    <t>Attack=7|AttackSpeed=0.055</t>
-  </si>
-  <si>
     <t>Rare_Glove_3</t>
   </si>
   <si>
     <t>Rare_Shoes_1</t>
   </si>
   <si>
-    <t>MoveSpeed=0.05|Evasion=3.0</t>
-  </si>
-  <si>
     <t>Rare_Shoes_2</t>
   </si>
   <si>
     <t>Rare_Shoes_3</t>
   </si>
   <si>
-    <t>MoveSpeed=0.055|Evasion=3.3</t>
-  </si>
-  <si>
     <t>Rare_Cape_1</t>
   </si>
   <si>
-    <t>HP=55|CritDmgIncrease=0.1</t>
-  </si>
-  <si>
     <t>Rare_Cape_2</t>
   </si>
   <si>
-    <t>HP=50|CritDmgIncrease=0.11</t>
-  </si>
-  <si>
     <t>Rare_Cape_3</t>
   </si>
   <si>
-    <t>HP=50|CritDmgIncrease=0.1</t>
-  </si>
-  <si>
     <t>Epic_Sword_1</t>
   </si>
   <si>
-    <t>Attack=15|AttackSpeed=0.045</t>
-  </si>
-  <si>
     <t>Epic_Sword_2</t>
   </si>
   <si>
-    <t>Attack=16|AttackSpeed=0.045</t>
-  </si>
-  <si>
     <t>Epic_Sword_3</t>
   </si>
   <si>
-    <t>Attack=15|CritChance=3.0</t>
-  </si>
-  <si>
     <t>Epic_Helmet_1</t>
   </si>
   <si>
@@ -391,69 +292,39 @@
     <t>Epic_Glove_1</t>
   </si>
   <si>
-    <t>Attack=9|AttackSpeed=0.075</t>
-  </si>
-  <si>
     <t>Epic_Glove_2</t>
   </si>
   <si>
-    <t>Attack=10|AttackSpeed=0.083</t>
-  </si>
-  <si>
     <t>Epic_Glove_3</t>
   </si>
   <si>
     <t>Epic_Shoes_1</t>
   </si>
   <si>
-    <t>MoveSpeed=0.075|Evasion=4.5</t>
-  </si>
-  <si>
     <t>Epic_Shoes_2</t>
   </si>
   <si>
     <t>Epic_Shoes_3</t>
   </si>
   <si>
-    <t>MoveSpeed=0.083|Evasion=4.95</t>
-  </si>
-  <si>
     <t>Epic_Cape_1</t>
   </si>
   <si>
-    <t>HP=82|CritDmgIncrease=0.15</t>
-  </si>
-  <si>
     <t>Epic_Cape_2</t>
   </si>
   <si>
-    <t>HP=75|CritDmgIncrease=0.165</t>
-  </si>
-  <si>
     <t>Epic_Cape_3</t>
   </si>
   <si>
-    <t>HP=75|CritDmgIncrease=0.15</t>
-  </si>
-  <si>
     <t>Legendary_Sword_1</t>
   </si>
   <si>
-    <t>Attack=22|AttackSpeed=0.066</t>
-  </si>
-  <si>
     <t>Legendary_Sword_2</t>
   </si>
   <si>
-    <t>Attack=24|AttackSpeed=0.066</t>
-  </si>
-  <si>
     <t>Legendary_Sword_3</t>
   </si>
   <si>
-    <t>Attack=22|CritChance=4.4</t>
-  </si>
-  <si>
     <t>Legendary_Helmet_1</t>
   </si>
   <si>
@@ -493,69 +364,39 @@
     <t>Legendary_Glove_1</t>
   </si>
   <si>
-    <t>Attack=13|AttackSpeed=0.11</t>
-  </si>
-  <si>
     <t>Legendary_Glove_2</t>
   </si>
   <si>
-    <t>Attack=15|AttackSpeed=0.121</t>
-  </si>
-  <si>
     <t>Legendary_Glove_3</t>
   </si>
   <si>
     <t>Legendary_Shoes_1</t>
   </si>
   <si>
-    <t>MoveSpeed=0.11|Evasion=6.6</t>
-  </si>
-  <si>
     <t>Legendary_Shoes_2</t>
   </si>
   <si>
     <t>Legendary_Shoes_3</t>
   </si>
   <si>
-    <t>MoveSpeed=0.121|Evasion=7.26</t>
-  </si>
-  <si>
     <t>Legendary_Cape_1</t>
   </si>
   <si>
-    <t>HP=121|CritDmgIncrease=0.22</t>
-  </si>
-  <si>
     <t>Legendary_Cape_2</t>
   </si>
   <si>
-    <t>HP=110|CritDmgIncrease=0.242</t>
-  </si>
-  <si>
     <t>Legendary_Cape_3</t>
   </si>
   <si>
-    <t>HP=110|CritDmgIncrease=0.22</t>
-  </si>
-  <si>
     <t>Mythic_Sword_1</t>
   </si>
   <si>
-    <t>Attack=32|AttackSpeed=0.096</t>
-  </si>
-  <si>
     <t>Mythic_Sword_2</t>
   </si>
   <si>
-    <t>Attack=35|AttackSpeed=0.096</t>
-  </si>
-  <si>
     <t>Mythic_Sword_3</t>
   </si>
   <si>
-    <t>Attack=32|CritChance=6.4</t>
-  </si>
-  <si>
     <t>Mythic_Helmet_1</t>
   </si>
   <si>
@@ -595,69 +436,39 @@
     <t>Mythic_Glove_1</t>
   </si>
   <si>
-    <t>Attack=19|AttackSpeed=0.16</t>
-  </si>
-  <si>
     <t>Mythic_Glove_2</t>
   </si>
   <si>
-    <t>Attack=21|AttackSpeed=0.176</t>
-  </si>
-  <si>
     <t>Mythic_Glove_3</t>
   </si>
   <si>
     <t>Mythic_Shoes_1</t>
   </si>
   <si>
-    <t>MoveSpeed=0.16|Evasion=9.6</t>
-  </si>
-  <si>
     <t>Mythic_Shoes_2</t>
   </si>
   <si>
     <t>Mythic_Shoes_3</t>
   </si>
   <si>
-    <t>MoveSpeed=0.176|Evasion=10.56</t>
-  </si>
-  <si>
     <t>Mythic_Cape_1</t>
   </si>
   <si>
-    <t>HP=176|CritDmgIncrease=0.32</t>
-  </si>
-  <si>
     <t>Mythic_Cape_2</t>
   </si>
   <si>
-    <t>HP=160|CritDmgIncrease=0.352</t>
-  </si>
-  <si>
     <t>Mythic_Cape_3</t>
   </si>
   <si>
-    <t>HP=160|CritDmgIncrease=0.32</t>
-  </si>
-  <si>
     <t>Special_Sword_1</t>
   </si>
   <si>
-    <t>Attack=45|AttackSpeed=0.135</t>
-  </si>
-  <si>
     <t>Special_Sword_2</t>
   </si>
   <si>
-    <t>Attack=50|AttackSpeed=0.135</t>
-  </si>
-  <si>
     <t>Special_Sword_3</t>
   </si>
   <si>
-    <t>Attack=45|CritChance=9.0</t>
-  </si>
-  <si>
     <t>Special_Helmet_1</t>
   </si>
   <si>
@@ -697,51 +508,30 @@
     <t>Special_Glove_1</t>
   </si>
   <si>
-    <t>Attack=27|AttackSpeed=0.225</t>
-  </si>
-  <si>
     <t>Special_Glove_2</t>
   </si>
   <si>
-    <t>Attack=30|AttackSpeed=0.248</t>
-  </si>
-  <si>
     <t>Special_Glove_3</t>
   </si>
   <si>
     <t>Special_Shoes_1</t>
   </si>
   <si>
-    <t>MoveSpeed=0.225|Evasion=13.5</t>
-  </si>
-  <si>
     <t>Special_Shoes_2</t>
   </si>
   <si>
     <t>Special_Shoes_3</t>
   </si>
   <si>
-    <t>MoveSpeed=0.248|Evasion=14.85</t>
-  </si>
-  <si>
     <t>Special_Cape_1</t>
   </si>
   <si>
-    <t>HP=248|CritDmgIncrease=0.45</t>
-  </si>
-  <si>
     <t>Special_Cape_2</t>
   </si>
   <si>
-    <t>HP=225|CritDmgIncrease=0.495</t>
-  </si>
-  <si>
     <t>Special_Cape_3</t>
   </si>
   <si>
-    <t>HP=225|CritDmgIncrease=0.45</t>
-  </si>
-  <si>
     <t>Sword</t>
   </si>
   <si>
@@ -758,6 +548,227 @@
   </si>
   <si>
     <t>Cape</t>
+  </si>
+  <si>
+    <t>Attack=6|AttackSpeed_Inc=0.018</t>
+  </si>
+  <si>
+    <t>Attack=7|AttackSpeed_Inc=0.018</t>
+  </si>
+  <si>
+    <t>Attack=4|AttackSpeed_Inc=0.03</t>
+  </si>
+  <si>
+    <t>Attack=4|AttackSpeed_Inc=0.033</t>
+  </si>
+  <si>
+    <t>Attack=8|AttackSpeed_Inc=0.024</t>
+  </si>
+  <si>
+    <t>Attack=9|AttackSpeed_Inc=0.024</t>
+  </si>
+  <si>
+    <t>Attack=5|AttackSpeed_Inc=0.04</t>
+  </si>
+  <si>
+    <t>Attack=5|AttackSpeed_Inc=0.044</t>
+  </si>
+  <si>
+    <t>Attack=10|AttackSpeed_Inc=0.03</t>
+  </si>
+  <si>
+    <t>Attack=11|AttackSpeed_Inc=0.03</t>
+  </si>
+  <si>
+    <t>Attack=6|AttackSpeed_Inc=0.05</t>
+  </si>
+  <si>
+    <t>Attack=7|AttackSpeed_Inc=0.055</t>
+  </si>
+  <si>
+    <t>Attack=15|AttackSpeed_Inc=0.045</t>
+  </si>
+  <si>
+    <t>Attack=16|AttackSpeed_Inc=0.045</t>
+  </si>
+  <si>
+    <t>Attack=9|AttackSpeed_Inc=0.075</t>
+  </si>
+  <si>
+    <t>Attack=10|AttackSpeed_Inc=0.083</t>
+  </si>
+  <si>
+    <t>Attack=22|AttackSpeed_Inc=0.066</t>
+  </si>
+  <si>
+    <t>Attack=24|AttackSpeed_Inc=0.066</t>
+  </si>
+  <si>
+    <t>Attack=13|AttackSpeed_Inc=0.11</t>
+  </si>
+  <si>
+    <t>Attack=15|AttackSpeed_Inc=0.121</t>
+  </si>
+  <si>
+    <t>Attack=32|AttackSpeed_Inc=0.096</t>
+  </si>
+  <si>
+    <t>Attack=35|AttackSpeed_Inc=0.096</t>
+  </si>
+  <si>
+    <t>Attack=19|AttackSpeed_Inc=0.16</t>
+  </si>
+  <si>
+    <t>Attack=21|AttackSpeed_Inc=0.176</t>
+  </si>
+  <si>
+    <t>Attack=45|AttackSpeed_Inc=0.135</t>
+  </si>
+  <si>
+    <t>Attack=50|AttackSpeed_Inc=0.135</t>
+  </si>
+  <si>
+    <t>Attack=27|AttackSpeed_Inc=0.225</t>
+  </si>
+  <si>
+    <t>Attack=30|AttackSpeed_Inc=0.248</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.225|Evasion=13.5</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.248|Evasion=14.85</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.03|Evasion=2</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.033|Evasion=2</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.04|Evasion=3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.044|Evasion=3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.05|Evasion=3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.055|Evasion=3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.075|Evasion=4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.083|Evasion=5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.11|Evasion=6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.121|Evasion=7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.16|Evasion=9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc=0.176|Evasion=10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP=33|CritDmg_Inc=0.06</t>
+  </si>
+  <si>
+    <t>HP=30|CritDmg_Inc=0.066</t>
+  </si>
+  <si>
+    <t>HP=30|CritDmg_Inc=0.06</t>
+  </si>
+  <si>
+    <t>HP=44|CritDmg_Inc=0.08</t>
+  </si>
+  <si>
+    <t>HP=40|CritDmg_Inc=0.08</t>
+  </si>
+  <si>
+    <t>HP=55|CritDmg_Inc=0.1</t>
+  </si>
+  <si>
+    <t>HP=50|CritDmg_Inc=0.11</t>
+  </si>
+  <si>
+    <t>HP=50|CritDmg_Inc=0.1</t>
+  </si>
+  <si>
+    <t>HP=82|CritDmg_Inc=0.15</t>
+  </si>
+  <si>
+    <t>HP=75|CritDmg_Inc=0.165</t>
+  </si>
+  <si>
+    <t>HP=75|CritDmg_Inc=0.15</t>
+  </si>
+  <si>
+    <t>HP=121|CritDmg_Inc=0.22</t>
+  </si>
+  <si>
+    <t>HP=110|CritDmg_Inc=0.242</t>
+  </si>
+  <si>
+    <t>HP=110|CritDmg_Inc=0.22</t>
+  </si>
+  <si>
+    <t>HP=176|CritDmg_Inc=0.32</t>
+  </si>
+  <si>
+    <t>HP=160|CritDmg_Inc=0.352</t>
+  </si>
+  <si>
+    <t>HP=160|CritDmg_Inc=0.32</t>
+  </si>
+  <si>
+    <t>HP=248|CritDmg_Inc=0.45</t>
+  </si>
+  <si>
+    <t>HP=225|CritDmg_Inc=0.495</t>
+  </si>
+  <si>
+    <t>HP=225|CritDmg_Inc=0.45</t>
+  </si>
+  <si>
+    <t>HP=40|CritDmg_Inc=0.088</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack=6|CritDmg_Inc=1.2</t>
+  </si>
+  <si>
+    <t>Attack=8|CritDmg_Inc=1.6</t>
+  </si>
+  <si>
+    <t>Attack=10|CritDmg_Inc=2.0</t>
+  </si>
+  <si>
+    <t>Attack=15|CritDmg_Inc=0.03</t>
+  </si>
+  <si>
+    <t>Attack=22|CritDmg_Inc=0.04</t>
+  </si>
+  <si>
+    <t>Attack=32|CritDmg_Inc=0.06</t>
+  </si>
+  <si>
+    <t>Attack=45|CritDmg_Inc=0.09</t>
   </si>
 </sst>
 </file>
@@ -1151,13 +1162,13 @@
         <v>3111</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1165,13 +1176,13 @@
         <v>3112</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1179,13 +1190,13 @@
         <v>3113</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1193,13 +1204,13 @@
         <v>3121</v>
       </c>
       <c r="B5" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1207,13 +1218,13 @@
         <v>3122</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1221,13 +1232,13 @@
         <v>3123</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1235,13 +1246,13 @@
         <v>3131</v>
       </c>
       <c r="B8" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1249,13 +1260,13 @@
         <v>3132</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1263,13 +1274,13 @@
         <v>3133</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1277,13 +1288,13 @@
         <v>3141</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1291,13 +1302,13 @@
         <v>3142</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1305,13 +1316,13 @@
         <v>3143</v>
       </c>
       <c r="B13" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1319,13 +1330,13 @@
         <v>3151</v>
       </c>
       <c r="B14" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1333,13 +1344,13 @@
         <v>3152</v>
       </c>
       <c r="B15" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1347,13 +1358,13 @@
         <v>3153</v>
       </c>
       <c r="B16" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1361,13 +1372,13 @@
         <v>3161</v>
       </c>
       <c r="B17" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1375,13 +1386,13 @@
         <v>3162</v>
       </c>
       <c r="B18" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1389,13 +1400,13 @@
         <v>3163</v>
       </c>
       <c r="B19" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1403,13 +1414,13 @@
         <v>3211</v>
       </c>
       <c r="B20" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1417,13 +1428,13 @@
         <v>3212</v>
       </c>
       <c r="B21" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1431,13 +1442,13 @@
         <v>3213</v>
       </c>
       <c r="B22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
         <v>240</v>
-      </c>
-      <c r="C22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1445,13 +1456,13 @@
         <v>3221</v>
       </c>
       <c r="B23" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1459,13 +1470,13 @@
         <v>3222</v>
       </c>
       <c r="B24" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1473,13 +1484,13 @@
         <v>3223</v>
       </c>
       <c r="B25" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1487,13 +1498,13 @@
         <v>3231</v>
       </c>
       <c r="B26" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1501,13 +1512,13 @@
         <v>3232</v>
       </c>
       <c r="B27" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1515,13 +1526,13 @@
         <v>3233</v>
       </c>
       <c r="B28" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1529,13 +1540,13 @@
         <v>3241</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1543,13 +1554,13 @@
         <v>3242</v>
       </c>
       <c r="B30" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1557,13 +1568,13 @@
         <v>3243</v>
       </c>
       <c r="B31" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1571,13 +1582,13 @@
         <v>3251</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1585,13 +1596,13 @@
         <v>3252</v>
       </c>
       <c r="B33" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C33" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1599,13 +1610,13 @@
         <v>3253</v>
       </c>
       <c r="B34" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>63</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1613,13 +1624,13 @@
         <v>3261</v>
       </c>
       <c r="B35" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1627,13 +1638,13 @@
         <v>3262</v>
       </c>
       <c r="B36" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1641,13 +1652,13 @@
         <v>3263</v>
       </c>
       <c r="B37" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>69</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1655,13 +1666,13 @@
         <v>3311</v>
       </c>
       <c r="B38" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1669,13 +1680,13 @@
         <v>3312</v>
       </c>
       <c r="B39" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D39" t="s">
-        <v>73</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1683,13 +1694,13 @@
         <v>3313</v>
       </c>
       <c r="B40" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1697,13 +1708,13 @@
         <v>3321</v>
       </c>
       <c r="B41" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C41" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1711,13 +1722,13 @@
         <v>3322</v>
       </c>
       <c r="B42" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1725,13 +1736,13 @@
         <v>3323</v>
       </c>
       <c r="B43" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1739,13 +1750,13 @@
         <v>3331</v>
       </c>
       <c r="B44" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C44" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1753,13 +1764,13 @@
         <v>3332</v>
       </c>
       <c r="B45" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1767,13 +1778,13 @@
         <v>3333</v>
       </c>
       <c r="B46" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C46" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1781,13 +1792,13 @@
         <v>3341</v>
       </c>
       <c r="B47" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C47" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="D47" t="s">
-        <v>89</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1795,13 +1806,13 @@
         <v>3342</v>
       </c>
       <c r="B48" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1809,13 +1820,13 @@
         <v>3343</v>
       </c>
       <c r="B49" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D49" t="s">
-        <v>89</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1823,13 +1834,13 @@
         <v>3351</v>
       </c>
       <c r="B50" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C50" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="D50" t="s">
-        <v>94</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1837,13 +1848,13 @@
         <v>3352</v>
       </c>
       <c r="B51" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D51" t="s">
-        <v>94</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1851,13 +1862,13 @@
         <v>3353</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1865,13 +1876,13 @@
         <v>3361</v>
       </c>
       <c r="B53" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C53" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1879,13 +1890,13 @@
         <v>3362</v>
       </c>
       <c r="B54" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C54" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1893,13 +1904,13 @@
         <v>3363</v>
       </c>
       <c r="B55" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C55" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>103</v>
+        <v>225</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1907,13 +1918,13 @@
         <v>3411</v>
       </c>
       <c r="B56" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C56" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D56" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1921,13 +1932,13 @@
         <v>3412</v>
       </c>
       <c r="B57" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="D57" t="s">
-        <v>107</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -1935,13 +1946,13 @@
         <v>3413</v>
       </c>
       <c r="B58" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C58" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="D58" t="s">
-        <v>109</v>
+        <v>242</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -1949,13 +1960,13 @@
         <v>3421</v>
       </c>
       <c r="B59" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C59" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="D59" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1963,13 +1974,13 @@
         <v>3422</v>
       </c>
       <c r="B60" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1977,13 +1988,13 @@
         <v>3423</v>
       </c>
       <c r="B61" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="D61" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -1991,13 +2002,13 @@
         <v>3431</v>
       </c>
       <c r="B62" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C62" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="D62" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -2005,13 +2016,13 @@
         <v>3432</v>
       </c>
       <c r="B63" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -2019,13 +2030,13 @@
         <v>3433</v>
       </c>
       <c r="B64" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C64" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="D64" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -2033,13 +2044,13 @@
         <v>3441</v>
       </c>
       <c r="B65" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="D65" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -2047,13 +2058,13 @@
         <v>3442</v>
       </c>
       <c r="B66" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C66" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="D66" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -2061,13 +2072,13 @@
         <v>3443</v>
       </c>
       <c r="B67" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="D67" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -2075,13 +2086,13 @@
         <v>3451</v>
       </c>
       <c r="B68" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C68" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="D68" t="s">
-        <v>128</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2089,13 +2100,13 @@
         <v>3452</v>
       </c>
       <c r="B69" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C69" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="D69" t="s">
-        <v>128</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -2103,13 +2114,13 @@
         <v>3453</v>
       </c>
       <c r="B70" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C70" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="D70" t="s">
-        <v>131</v>
+        <v>213</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -2117,13 +2128,13 @@
         <v>3461</v>
       </c>
       <c r="B71" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C71" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="D71" t="s">
-        <v>133</v>
+        <v>226</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -2131,13 +2142,13 @@
         <v>3462</v>
       </c>
       <c r="B72" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C72" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="D72" t="s">
-        <v>135</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -2145,13 +2156,13 @@
         <v>3463</v>
       </c>
       <c r="B73" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C73" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="D73" t="s">
-        <v>137</v>
+        <v>228</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -2159,13 +2170,13 @@
         <v>3511</v>
       </c>
       <c r="B74" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="D74" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -2173,13 +2184,13 @@
         <v>3512</v>
       </c>
       <c r="B75" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="D75" t="s">
-        <v>141</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -2187,13 +2198,13 @@
         <v>3513</v>
       </c>
       <c r="B76" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="D76" t="s">
-        <v>143</v>
+        <v>243</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -2201,13 +2212,13 @@
         <v>3521</v>
       </c>
       <c r="B77" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C77" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="D77" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -2215,13 +2226,13 @@
         <v>3522</v>
       </c>
       <c r="B78" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C78" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="D78" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -2229,13 +2240,13 @@
         <v>3523</v>
       </c>
       <c r="B79" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C79" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="D79" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -2243,13 +2254,13 @@
         <v>3531</v>
       </c>
       <c r="B80" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C80" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="D80" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -2257,13 +2268,13 @@
         <v>3532</v>
       </c>
       <c r="B81" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C81" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="D81" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -2271,13 +2282,13 @@
         <v>3533</v>
       </c>
       <c r="B82" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="D82" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -2285,13 +2296,13 @@
         <v>3541</v>
       </c>
       <c r="B83" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C83" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="D83" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -2299,13 +2310,13 @@
         <v>3542</v>
       </c>
       <c r="B84" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C84" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="D84" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -2313,13 +2324,13 @@
         <v>3543</v>
       </c>
       <c r="B85" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C85" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="D85" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -2327,13 +2338,13 @@
         <v>3551</v>
       </c>
       <c r="B86" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C86" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="D86" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -2341,13 +2352,13 @@
         <v>3552</v>
       </c>
       <c r="B87" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C87" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="D87" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -2355,13 +2366,13 @@
         <v>3553</v>
       </c>
       <c r="B88" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C88" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -2369,13 +2380,13 @@
         <v>3561</v>
       </c>
       <c r="B89" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C89" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="D89" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -2383,13 +2394,13 @@
         <v>3562</v>
       </c>
       <c r="B90" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C90" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="D90" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -2397,13 +2408,13 @@
         <v>3563</v>
       </c>
       <c r="B91" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C91" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="D91" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -2411,13 +2422,13 @@
         <v>3611</v>
       </c>
       <c r="B92" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C92" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="D92" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -2425,13 +2436,13 @@
         <v>3612</v>
       </c>
       <c r="B93" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C93" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="D93" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -2439,13 +2450,13 @@
         <v>3613</v>
       </c>
       <c r="B94" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C94" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -2453,13 +2464,13 @@
         <v>3621</v>
       </c>
       <c r="B95" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C95" t="s">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="D95" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -2467,13 +2478,13 @@
         <v>3622</v>
       </c>
       <c r="B96" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C96" t="s">
-        <v>180</v>
+        <v>127</v>
       </c>
       <c r="D96" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -2481,13 +2492,13 @@
         <v>3623</v>
       </c>
       <c r="B97" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C97" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="D97" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -2495,13 +2506,13 @@
         <v>3631</v>
       </c>
       <c r="B98" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C98" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="D98" t="s">
-        <v>185</v>
+        <v>132</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -2509,13 +2520,13 @@
         <v>3632</v>
       </c>
       <c r="B99" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C99" t="s">
-        <v>186</v>
+        <v>133</v>
       </c>
       <c r="D99" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -2523,13 +2534,13 @@
         <v>3633</v>
       </c>
       <c r="B100" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C100" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="D100" t="s">
-        <v>189</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -2537,13 +2548,13 @@
         <v>3641</v>
       </c>
       <c r="B101" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C101" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="D101" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -2551,13 +2562,13 @@
         <v>3642</v>
       </c>
       <c r="B102" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C102" t="s">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="D102" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -2565,13 +2576,13 @@
         <v>3643</v>
       </c>
       <c r="B103" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C103" t="s">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="D103" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -2579,13 +2590,13 @@
         <v>3651</v>
       </c>
       <c r="B104" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C104" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="D104" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -2593,13 +2604,13 @@
         <v>3652</v>
       </c>
       <c r="B105" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C105" t="s">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="D105" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -2607,13 +2618,13 @@
         <v>3653</v>
       </c>
       <c r="B106" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C106" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="D106" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -2621,13 +2632,13 @@
         <v>3661</v>
       </c>
       <c r="B107" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C107" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="D107" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -2635,13 +2646,13 @@
         <v>3662</v>
       </c>
       <c r="B108" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C108" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="D108" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -2649,13 +2660,13 @@
         <v>3663</v>
       </c>
       <c r="B109" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C109" t="s">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="D109" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -2663,13 +2674,13 @@
         <v>3711</v>
       </c>
       <c r="B110" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C110" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="D110" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -2677,13 +2688,13 @@
         <v>3712</v>
       </c>
       <c r="B111" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C111" t="s">
-        <v>208</v>
+        <v>147</v>
       </c>
       <c r="D111" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -2691,13 +2702,13 @@
         <v>3713</v>
       </c>
       <c r="B112" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C112" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="D112" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -2705,13 +2716,13 @@
         <v>3721</v>
       </c>
       <c r="B113" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C113" t="s">
-        <v>212</v>
+        <v>149</v>
       </c>
       <c r="D113" t="s">
-        <v>213</v>
+        <v>150</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -2719,13 +2730,13 @@
         <v>3722</v>
       </c>
       <c r="B114" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C114" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="D114" t="s">
-        <v>215</v>
+        <v>152</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -2733,13 +2744,13 @@
         <v>3723</v>
       </c>
       <c r="B115" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C115" t="s">
-        <v>216</v>
+        <v>153</v>
       </c>
       <c r="D115" t="s">
-        <v>217</v>
+        <v>154</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -2747,13 +2758,13 @@
         <v>3731</v>
       </c>
       <c r="B116" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C116" t="s">
-        <v>218</v>
+        <v>155</v>
       </c>
       <c r="D116" t="s">
-        <v>219</v>
+        <v>156</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -2761,13 +2772,13 @@
         <v>3732</v>
       </c>
       <c r="B117" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C117" t="s">
-        <v>220</v>
+        <v>157</v>
       </c>
       <c r="D117" t="s">
-        <v>221</v>
+        <v>158</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -2775,13 +2786,13 @@
         <v>3733</v>
       </c>
       <c r="B118" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C118" t="s">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="D118" t="s">
-        <v>223</v>
+        <v>160</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -2789,13 +2800,13 @@
         <v>3741</v>
       </c>
       <c r="B119" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C119" t="s">
-        <v>224</v>
+        <v>161</v>
       </c>
       <c r="D119" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -2803,13 +2814,13 @@
         <v>3742</v>
       </c>
       <c r="B120" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C120" t="s">
-        <v>226</v>
+        <v>162</v>
       </c>
       <c r="D120" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -2817,13 +2828,13 @@
         <v>3743</v>
       </c>
       <c r="B121" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="C121" t="s">
-        <v>228</v>
+        <v>163</v>
       </c>
       <c r="D121" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -2831,13 +2842,13 @@
         <v>3751</v>
       </c>
       <c r="B122" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C122" t="s">
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="D122" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -2845,13 +2856,13 @@
         <v>3752</v>
       </c>
       <c r="B123" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C123" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
       <c r="D123" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -2859,13 +2870,13 @@
         <v>3753</v>
       </c>
       <c r="B124" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C124" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="D124" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -2873,10 +2884,10 @@
         <v>3761</v>
       </c>
       <c r="B125" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C125" t="s">
-        <v>234</v>
+        <v>167</v>
       </c>
       <c r="D125" t="s">
         <v>235</v>
@@ -2887,13 +2898,13 @@
         <v>3762</v>
       </c>
       <c r="B126" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C126" t="s">
+        <v>168</v>
+      </c>
+      <c r="D126" t="s">
         <v>236</v>
-      </c>
-      <c r="D126" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -2901,13 +2912,13 @@
         <v>3763</v>
       </c>
       <c r="B127" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C127" t="s">
-        <v>238</v>
+        <v>169</v>
       </c>
       <c r="D127" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Equip.xlsx
+++ b/Data/Equip.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7190AF-29F0-41C4-8BF3-942956568415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA64AE9-B763-4943-BEFC-690C5A407FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8460" yWindow="2835" windowWidth="21645" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equip" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -34,15 +47,6 @@
     <t>BaseStats</t>
   </si>
   <si>
-    <t>Common_Sword_1</t>
-  </si>
-  <si>
-    <t>Common_Sword_2</t>
-  </si>
-  <si>
-    <t>Common_Sword_3</t>
-  </si>
-  <si>
     <t>Common_Helmet_1</t>
   </si>
   <si>
@@ -103,15 +107,6 @@
     <t>Common_Cape_3</t>
   </si>
   <si>
-    <t>Uncommon_Sword_1</t>
-  </si>
-  <si>
-    <t>Uncommon_Sword_2</t>
-  </si>
-  <si>
-    <t>Uncommon_Sword_3</t>
-  </si>
-  <si>
     <t>Uncommon_Helmet_1</t>
   </si>
   <si>
@@ -172,15 +167,6 @@
     <t>Uncommon_Cape_3</t>
   </si>
   <si>
-    <t>Rare_Sword_1</t>
-  </si>
-  <si>
-    <t>Rare_Sword_2</t>
-  </si>
-  <si>
-    <t>Rare_Sword_3</t>
-  </si>
-  <si>
     <t>Rare_Helmet_1</t>
   </si>
   <si>
@@ -244,15 +230,6 @@
     <t>Rare_Cape_3</t>
   </si>
   <si>
-    <t>Epic_Sword_1</t>
-  </si>
-  <si>
-    <t>Epic_Sword_2</t>
-  </si>
-  <si>
-    <t>Epic_Sword_3</t>
-  </si>
-  <si>
     <t>Epic_Helmet_1</t>
   </si>
   <si>
@@ -316,15 +293,6 @@
     <t>Epic_Cape_3</t>
   </si>
   <si>
-    <t>Legendary_Sword_1</t>
-  </si>
-  <si>
-    <t>Legendary_Sword_2</t>
-  </si>
-  <si>
-    <t>Legendary_Sword_3</t>
-  </si>
-  <si>
     <t>Legendary_Helmet_1</t>
   </si>
   <si>
@@ -388,15 +356,6 @@
     <t>Legendary_Cape_3</t>
   </si>
   <si>
-    <t>Mythic_Sword_1</t>
-  </si>
-  <si>
-    <t>Mythic_Sword_2</t>
-  </si>
-  <si>
-    <t>Mythic_Sword_3</t>
-  </si>
-  <si>
     <t>Mythic_Helmet_1</t>
   </si>
   <si>
@@ -460,15 +419,6 @@
     <t>Mythic_Cape_3</t>
   </si>
   <si>
-    <t>Special_Sword_1</t>
-  </si>
-  <si>
-    <t>Special_Sword_2</t>
-  </si>
-  <si>
-    <t>Special_Sword_3</t>
-  </si>
-  <si>
     <t>Special_Helmet_1</t>
   </si>
   <si>
@@ -532,9 +482,6 @@
     <t>Special_Cape_3</t>
   </si>
   <si>
-    <t>Sword</t>
-  </si>
-  <si>
     <t>Helmet</t>
   </si>
   <si>
@@ -548,9 +495,6 @@
   </si>
   <si>
     <t>Cape</t>
-  </si>
-  <si>
-    <t>Attack=6|AttackSpeed_Inc=0.018</t>
   </si>
   <si>
     <t>Attack=7|AttackSpeed_Inc=0.018</t>
@@ -769,6 +713,76 @@
   </si>
   <si>
     <t>Attack=45|CritDmg_Inc=0.09</t>
+  </si>
+  <si>
+    <t>Bow</t>
+  </si>
+  <si>
+    <t>Common_Bow_1</t>
+  </si>
+  <si>
+    <t>Common_Bow_2</t>
+  </si>
+  <si>
+    <t>Common_Bow_3</t>
+  </si>
+  <si>
+    <t>Uncommon_Bow_1</t>
+  </si>
+  <si>
+    <t>Uncommon_Bow_2</t>
+  </si>
+  <si>
+    <t>Uncommon_Bow_3</t>
+  </si>
+  <si>
+    <t>Rare_Bow_1</t>
+  </si>
+  <si>
+    <t>Rare_Bow_2</t>
+  </si>
+  <si>
+    <t>Rare_Bow_3</t>
+  </si>
+  <si>
+    <t>Epic_Bow_1</t>
+  </si>
+  <si>
+    <t>Epic_Bow_2</t>
+  </si>
+  <si>
+    <t>Epic_Bow_3</t>
+  </si>
+  <si>
+    <t>Legendary_Bow_1</t>
+  </si>
+  <si>
+    <t>Legendary_Bow_2</t>
+  </si>
+  <si>
+    <t>Legendary_Bow_3</t>
+  </si>
+  <si>
+    <t>Mythic_Bow_1</t>
+  </si>
+  <si>
+    <t>Mythic_Bow_2</t>
+  </si>
+  <si>
+    <t>Mythic_Bow_3</t>
+  </si>
+  <si>
+    <t>Special_Bow_1</t>
+  </si>
+  <si>
+    <t>Special_Bow_2</t>
+  </si>
+  <si>
+    <t>Special_Bow_3</t>
+  </si>
+  <si>
+    <t>Attack=6|AttackSpeed_Inc=0.018</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1142,6 +1156,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D127"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1162,13 +1179,13 @@
         <v>3111</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1176,13 +1193,13 @@
         <v>3112</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1190,13 +1207,13 @@
         <v>3113</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
       <c r="D4" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1204,13 +1221,13 @@
         <v>3121</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1218,13 +1235,13 @@
         <v>3122</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1232,13 +1249,13 @@
         <v>3123</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1246,13 +1263,13 @@
         <v>3131</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1260,13 +1277,13 @@
         <v>3132</v>
       </c>
       <c r="B9" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1274,13 +1291,13 @@
         <v>3133</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1288,13 +1305,13 @@
         <v>3141</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1302,13 +1319,13 @@
         <v>3142</v>
       </c>
       <c r="B12" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1316,13 +1333,13 @@
         <v>3143</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1330,13 +1347,13 @@
         <v>3151</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1344,13 +1361,13 @@
         <v>3152</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1358,13 +1375,13 @@
         <v>3153</v>
       </c>
       <c r="B16" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1372,13 +1389,13 @@
         <v>3161</v>
       </c>
       <c r="B17" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1386,13 +1403,13 @@
         <v>3162</v>
       </c>
       <c r="B18" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1400,13 +1417,13 @@
         <v>3163</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1414,13 +1431,13 @@
         <v>3211</v>
       </c>
       <c r="B20" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="D20" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1428,13 +1445,13 @@
         <v>3212</v>
       </c>
       <c r="B21" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>228</v>
       </c>
       <c r="D21" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1442,13 +1459,13 @@
         <v>3213</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>229</v>
       </c>
       <c r="D22" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1456,13 +1473,13 @@
         <v>3221</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1470,13 +1487,13 @@
         <v>3222</v>
       </c>
       <c r="B24" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1484,13 +1501,13 @@
         <v>3223</v>
       </c>
       <c r="B25" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1498,13 +1515,13 @@
         <v>3231</v>
       </c>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1512,13 +1529,13 @@
         <v>3232</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1526,13 +1543,13 @@
         <v>3233</v>
       </c>
       <c r="B28" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1540,13 +1557,13 @@
         <v>3241</v>
       </c>
       <c r="B29" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1554,13 +1571,13 @@
         <v>3242</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1568,13 +1585,13 @@
         <v>3243</v>
       </c>
       <c r="B31" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1582,13 +1599,13 @@
         <v>3251</v>
       </c>
       <c r="B32" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1596,13 +1613,13 @@
         <v>3252</v>
       </c>
       <c r="B33" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1610,13 +1627,13 @@
         <v>3253</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1624,13 +1641,13 @@
         <v>3261</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1638,13 +1655,13 @@
         <v>3262</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D36" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1652,13 +1669,13 @@
         <v>3263</v>
       </c>
       <c r="B37" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1666,13 +1683,13 @@
         <v>3311</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="D38" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1680,13 +1697,13 @@
         <v>3312</v>
       </c>
       <c r="B39" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C39" t="s">
-        <v>51</v>
+        <v>231</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1694,13 +1711,13 @@
         <v>3313</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>232</v>
       </c>
       <c r="D40" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1708,13 +1725,13 @@
         <v>3321</v>
       </c>
       <c r="B41" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1722,13 +1739,13 @@
         <v>3322</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1736,13 +1753,13 @@
         <v>3323</v>
       </c>
       <c r="B43" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1750,13 +1767,13 @@
         <v>3331</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1764,13 +1781,13 @@
         <v>3332</v>
       </c>
       <c r="B45" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1778,13 +1795,13 @@
         <v>3333</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1792,13 +1809,13 @@
         <v>3341</v>
       </c>
       <c r="B47" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C47" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1806,13 +1823,13 @@
         <v>3342</v>
       </c>
       <c r="B48" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D48" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1820,13 +1837,13 @@
         <v>3343</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C49" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1834,13 +1851,13 @@
         <v>3351</v>
       </c>
       <c r="B50" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D50" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1848,13 +1865,13 @@
         <v>3352</v>
       </c>
       <c r="B51" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D51" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1862,13 +1879,13 @@
         <v>3353</v>
       </c>
       <c r="B52" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D52" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1876,13 +1893,13 @@
         <v>3361</v>
       </c>
       <c r="B53" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1890,13 +1907,13 @@
         <v>3362</v>
       </c>
       <c r="B54" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D54" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1904,13 +1921,13 @@
         <v>3363</v>
       </c>
       <c r="B55" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D55" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1918,13 +1935,13 @@
         <v>3411</v>
       </c>
       <c r="B56" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C56" t="s">
-        <v>74</v>
+        <v>233</v>
       </c>
       <c r="D56" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1932,13 +1949,13 @@
         <v>3412</v>
       </c>
       <c r="B57" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C57" t="s">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="D57" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -1946,13 +1963,13 @@
         <v>3413</v>
       </c>
       <c r="B58" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C58" t="s">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="D58" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -1960,13 +1977,13 @@
         <v>3421</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C59" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D59" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1974,13 +1991,13 @@
         <v>3422</v>
       </c>
       <c r="B60" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D60" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1988,13 +2005,13 @@
         <v>3423</v>
       </c>
       <c r="B61" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C61" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D61" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -2002,13 +2019,13 @@
         <v>3431</v>
       </c>
       <c r="B62" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C62" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D62" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -2016,13 +2033,13 @@
         <v>3432</v>
       </c>
       <c r="B63" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C63" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -2030,13 +2047,13 @@
         <v>3433</v>
       </c>
       <c r="B64" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C64" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D64" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -2044,13 +2061,13 @@
         <v>3441</v>
       </c>
       <c r="B65" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C65" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D65" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -2058,13 +2075,13 @@
         <v>3442</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D66" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -2072,13 +2089,13 @@
         <v>3443</v>
       </c>
       <c r="B67" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C67" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D67" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -2086,13 +2103,13 @@
         <v>3451</v>
       </c>
       <c r="B68" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D68" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2100,13 +2117,13 @@
         <v>3452</v>
       </c>
       <c r="B69" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C69" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D69" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -2114,13 +2131,13 @@
         <v>3453</v>
       </c>
       <c r="B70" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C70" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D70" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -2128,13 +2145,13 @@
         <v>3461</v>
       </c>
       <c r="B71" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C71" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D71" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -2142,13 +2159,13 @@
         <v>3462</v>
       </c>
       <c r="B72" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D72" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -2156,13 +2173,13 @@
         <v>3463</v>
       </c>
       <c r="B73" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D73" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -2170,13 +2187,13 @@
         <v>3511</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C74" t="s">
-        <v>98</v>
+        <v>236</v>
       </c>
       <c r="D74" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -2184,13 +2201,13 @@
         <v>3512</v>
       </c>
       <c r="B75" t="s">
+        <v>223</v>
+      </c>
+      <c r="C75" t="s">
+        <v>237</v>
+      </c>
+      <c r="D75" t="s">
         <v>170</v>
-      </c>
-      <c r="C75" t="s">
-        <v>99</v>
-      </c>
-      <c r="D75" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -2198,13 +2215,13 @@
         <v>3513</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C76" t="s">
-        <v>100</v>
+        <v>238</v>
       </c>
       <c r="D76" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -2212,13 +2229,13 @@
         <v>3521</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="D77" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -2226,13 +2243,13 @@
         <v>3522</v>
       </c>
       <c r="B78" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C78" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D78" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -2240,13 +2257,13 @@
         <v>3523</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C79" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D79" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -2254,13 +2271,13 @@
         <v>3531</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D80" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -2268,13 +2285,13 @@
         <v>3532</v>
       </c>
       <c r="B81" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C81" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D81" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -2282,13 +2299,13 @@
         <v>3533</v>
       </c>
       <c r="B82" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C82" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D82" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -2296,13 +2313,13 @@
         <v>3541</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C83" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D83" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -2310,13 +2327,13 @@
         <v>3542</v>
       </c>
       <c r="B84" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C84" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D84" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -2324,13 +2341,13 @@
         <v>3543</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C85" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D85" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -2338,13 +2355,13 @@
         <v>3551</v>
       </c>
       <c r="B86" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C86" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D86" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -2352,13 +2369,13 @@
         <v>3552</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C87" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D87" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -2366,13 +2383,13 @@
         <v>3553</v>
       </c>
       <c r="B88" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D88" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -2380,13 +2397,13 @@
         <v>3561</v>
       </c>
       <c r="B89" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C89" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D89" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -2394,13 +2411,13 @@
         <v>3562</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C90" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D90" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -2408,13 +2425,13 @@
         <v>3563</v>
       </c>
       <c r="B91" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C91" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D91" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -2422,13 +2439,13 @@
         <v>3611</v>
       </c>
       <c r="B92" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C92" t="s">
-        <v>122</v>
+        <v>239</v>
       </c>
       <c r="D92" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -2436,13 +2453,13 @@
         <v>3612</v>
       </c>
       <c r="B93" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C93" t="s">
-        <v>123</v>
+        <v>240</v>
       </c>
       <c r="D93" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -2450,13 +2467,13 @@
         <v>3613</v>
       </c>
       <c r="B94" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C94" t="s">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="D94" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -2464,13 +2481,13 @@
         <v>3621</v>
       </c>
       <c r="B95" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C95" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D95" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -2478,13 +2495,13 @@
         <v>3622</v>
       </c>
       <c r="B96" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C96" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D96" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -2492,13 +2509,13 @@
         <v>3623</v>
       </c>
       <c r="B97" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D97" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -2506,13 +2523,13 @@
         <v>3631</v>
       </c>
       <c r="B98" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C98" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="D98" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -2520,13 +2537,13 @@
         <v>3632</v>
       </c>
       <c r="B99" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C99" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D99" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -2534,13 +2551,13 @@
         <v>3633</v>
       </c>
       <c r="B100" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C100" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -2548,13 +2565,13 @@
         <v>3641</v>
       </c>
       <c r="B101" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C101" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D101" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -2562,13 +2579,13 @@
         <v>3642</v>
       </c>
       <c r="B102" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C102" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="D102" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -2576,13 +2593,13 @@
         <v>3643</v>
       </c>
       <c r="B103" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C103" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="D103" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -2590,13 +2607,13 @@
         <v>3651</v>
       </c>
       <c r="B104" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C104" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D104" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -2604,13 +2621,13 @@
         <v>3652</v>
       </c>
       <c r="B105" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C105" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="D105" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -2618,13 +2635,13 @@
         <v>3653</v>
       </c>
       <c r="B106" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C106" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D106" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -2632,13 +2649,13 @@
         <v>3661</v>
       </c>
       <c r="B107" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C107" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D107" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -2646,13 +2663,13 @@
         <v>3662</v>
       </c>
       <c r="B108" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C108" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D108" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -2660,13 +2677,13 @@
         <v>3663</v>
       </c>
       <c r="B109" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C109" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D109" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -2674,13 +2691,13 @@
         <v>3711</v>
       </c>
       <c r="B110" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
+        <v>242</v>
       </c>
       <c r="D110" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -2688,13 +2705,13 @@
         <v>3712</v>
       </c>
       <c r="B111" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C111" t="s">
-        <v>147</v>
+        <v>243</v>
       </c>
       <c r="D111" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -2702,13 +2719,13 @@
         <v>3713</v>
       </c>
       <c r="B112" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C112" t="s">
-        <v>148</v>
+        <v>244</v>
       </c>
       <c r="D112" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -2716,13 +2733,13 @@
         <v>3721</v>
       </c>
       <c r="B113" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C113" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="D113" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -2730,13 +2747,13 @@
         <v>3722</v>
       </c>
       <c r="B114" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C114" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="D114" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -2744,13 +2761,13 @@
         <v>3723</v>
       </c>
       <c r="B115" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C115" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D115" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -2758,13 +2775,13 @@
         <v>3731</v>
       </c>
       <c r="B116" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C116" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D116" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -2772,13 +2789,13 @@
         <v>3732</v>
       </c>
       <c r="B117" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C117" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D117" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -2786,13 +2803,13 @@
         <v>3733</v>
       </c>
       <c r="B118" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C118" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D118" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -2800,13 +2817,13 @@
         <v>3741</v>
       </c>
       <c r="B119" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C119" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="D119" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -2814,13 +2831,13 @@
         <v>3742</v>
       </c>
       <c r="B120" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C120" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="D120" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -2828,13 +2845,13 @@
         <v>3743</v>
       </c>
       <c r="B121" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C121" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D121" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -2842,13 +2859,13 @@
         <v>3751</v>
       </c>
       <c r="B122" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C122" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D122" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -2856,13 +2873,13 @@
         <v>3752</v>
       </c>
       <c r="B123" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C123" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D123" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -2870,13 +2887,13 @@
         <v>3753</v>
       </c>
       <c r="B124" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C124" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D124" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -2884,13 +2901,13 @@
         <v>3761</v>
       </c>
       <c r="B125" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C125" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="D125" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -2898,13 +2915,13 @@
         <v>3762</v>
       </c>
       <c r="B126" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C126" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D126" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -2912,13 +2929,13 @@
         <v>3763</v>
       </c>
       <c r="B127" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C127" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D127" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
